--- a/A_Documentation/Rapport/assets/annexes/BOM.xlsx
+++ b/A_Documentation/Rapport/assets/annexes/BOM.xlsx
@@ -5,22 +5,35 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerem\Documents\Repositories\Self-Balancing-Bot\A_Documentation\Rapport\assets\figures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerem\Documents\Repositories\Self-Balancing-Bot\A_Documentation\Rapport\assets\annexes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{2E6DDC4E-765D-4E33-B0CD-8EDF4B70E88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D0B760-793D-4427-A7F1-2731C492B411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AF9B6FE-E1EB-492A-BAD0-33829DC36424}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="103">
   <si>
     <t>Reference</t>
   </si>
@@ -236,16 +249,110 @@
   </si>
   <si>
     <t>JLCPCB</t>
+  </si>
+  <si>
+    <t>Vis tête cylindrique</t>
+  </si>
+  <si>
+    <t>(MakeLab)</t>
+  </si>
+  <si>
+    <t>M3x6mm</t>
+  </si>
+  <si>
+    <t>M3x12mm</t>
+  </si>
+  <si>
+    <t>M3x8mm</t>
+  </si>
+  <si>
+    <t>M3x10mm</t>
+  </si>
+  <si>
+    <t>M3x5mm</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Ecrou M3</t>
+  </si>
+  <si>
+    <t>Atelier Mécanique</t>
+  </si>
+  <si>
+    <t>Coupleur</t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>Wenzhou Wancheng Machinery Store</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Batterie LiPo 4s</t>
+  </si>
+  <si>
+    <t>SwayTronic</t>
+  </si>
+  <si>
+    <t>Câble XT60</t>
+  </si>
+  <si>
+    <t>7640159361831</t>
+  </si>
+  <si>
+    <t>7640182620691</t>
+  </si>
+  <si>
+    <t>Moteur pas à pas</t>
+  </si>
+  <si>
+    <t>NEMA17-04</t>
+  </si>
+  <si>
+    <t>Brack</t>
+  </si>
+  <si>
+    <t>126042</t>
+  </si>
+  <si>
+    <t>MECA</t>
+  </si>
+  <si>
+    <t>ALIM+MOT</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Colonnette</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="8" formatCode="&quot;CHF&quot;\ #,##0.00;[Red]&quot;CHF&quot;\ \-#,##0.00"/>
+    <numFmt numFmtId="184" formatCode="0.00000000000000000E+00"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -395,8 +502,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -582,8 +696,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -750,6 +876,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -795,7 +958,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -809,6 +972,34 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="19" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="184" fontId="19" fillId="35" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="19" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="8" fontId="19" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="19" fillId="35" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1185,20 +1376,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DC2B278-CA9F-41CF-928A-21BFBDC569B1}">
-  <dimension ref="A1:K13"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="3.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="8.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
@@ -1266,6 +1459,7 @@
         <v>0.34</v>
       </c>
       <c r="J2" s="4">
+        <f>H2*I2</f>
         <v>0.68</v>
       </c>
       <c r="K2" s="5" t="s">
@@ -1301,7 +1495,8 @@
         <v>2.46</v>
       </c>
       <c r="J3" s="4">
-        <v>2.46</v>
+        <f t="shared" ref="J3:J18" si="0">H3*I3</f>
+        <v>4.92</v>
       </c>
       <c r="K3" s="6"/>
     </row>
@@ -1334,6 +1529,7 @@
         <v>0.26</v>
       </c>
       <c r="J4" s="4">
+        <f t="shared" si="0"/>
         <v>0.26</v>
       </c>
       <c r="K4" s="6"/>
@@ -1367,6 +1563,7 @@
         <v>0.08</v>
       </c>
       <c r="J5" s="4">
+        <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
       <c r="K5" s="6"/>
@@ -1400,6 +1597,7 @@
         <v>0.08</v>
       </c>
       <c r="J6" s="4">
+        <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
       <c r="K6" s="6"/>
@@ -1433,6 +1631,7 @@
         <v>0.08</v>
       </c>
       <c r="J7" s="4">
+        <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
       <c r="K7" s="6"/>
@@ -1466,6 +1665,7 @@
         <v>0.65</v>
       </c>
       <c r="J8" s="4">
+        <f t="shared" si="0"/>
         <v>0.65</v>
       </c>
       <c r="K8" s="6"/>
@@ -1499,6 +1699,7 @@
         <v>4.53</v>
       </c>
       <c r="J9" s="4">
+        <f t="shared" si="0"/>
         <v>4.53</v>
       </c>
       <c r="K9" s="6"/>
@@ -1532,6 +1733,7 @@
         <v>16.93</v>
       </c>
       <c r="J10" s="4">
+        <f t="shared" si="0"/>
         <v>16.93</v>
       </c>
       <c r="K10" s="6"/>
@@ -1565,6 +1767,7 @@
         <v>7.7</v>
       </c>
       <c r="J11" s="4">
+        <f t="shared" si="0"/>
         <v>15.4</v>
       </c>
       <c r="K11" s="6"/>
@@ -1598,6 +1801,7 @@
         <v>4.2</v>
       </c>
       <c r="J12" s="4">
+        <f t="shared" si="0"/>
         <v>4.2</v>
       </c>
       <c r="K12" s="7"/>
@@ -1631,17 +1835,377 @@
         <v>1.4</v>
       </c>
       <c r="J13" s="4">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="K13" s="4">
         <v>52.35</v>
       </c>
     </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14" s="9">
+        <v>12</v>
+      </c>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="9">
+        <v>4</v>
+      </c>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="15"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="9">
+        <v>4</v>
+      </c>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="15"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H17" s="9">
+        <v>16</v>
+      </c>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="15"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" s="9">
+        <v>4</v>
+      </c>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="15"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H19" s="9">
+        <v>2</v>
+      </c>
+      <c r="I19" s="10">
+        <v>2.57</v>
+      </c>
+      <c r="J19" s="10">
+        <f t="shared" ref="J19" si="1">H19*I19</f>
+        <v>5.14</v>
+      </c>
+      <c r="K19" s="15"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H20" s="9">
+        <v>4</v>
+      </c>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10">
+        <f t="shared" ref="J20:J21" si="2">H20*I20</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="10">
+        <f>SUM(J14:J20)</f>
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="H21" s="11">
+        <v>1</v>
+      </c>
+      <c r="I21" s="13">
+        <v>31.25</v>
+      </c>
+      <c r="J21" s="13">
+        <f t="shared" si="2"/>
+        <v>31.25</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="H22" s="11">
+        <v>1</v>
+      </c>
+      <c r="I22" s="13">
+        <v>5.3</v>
+      </c>
+      <c r="J22" s="13">
+        <f t="shared" ref="J22" si="3">H22*I22</f>
+        <v>5.3</v>
+      </c>
+      <c r="K22" s="17"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="H23" s="11">
+        <v>1</v>
+      </c>
+      <c r="I23" s="13">
+        <v>15.95</v>
+      </c>
+      <c r="J23" s="13">
+        <f t="shared" ref="J23" si="4">H23*I23</f>
+        <v>15.95</v>
+      </c>
+      <c r="K23" s="13">
+        <f>SUM(J21:J23)</f>
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="21">
+        <f>SUM(K23,K20,K13)</f>
+        <v>109.99000000000001</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
     <mergeCell ref="K2:K12"/>
+    <mergeCell ref="K14:K19"/>
+    <mergeCell ref="K21:K22"/>
+    <mergeCell ref="A24:J24"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
+  <pageSetup scale="94" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>